--- a/output/pdf_financials_xlsx/PSK.xlsx
+++ b/output/pdf_financials_xlsx/PSK.xlsx
@@ -3241,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>34.6</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>44.2</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="65">
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>0</v>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0.021</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.0271</v>
+        <v>0.0265</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.0242</v>
@@ -3936,10 +3936,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.000241380697590216</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
@@ -5097,7 +5095,7 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -13812,7 +13810,11 @@
           <t>Current portion of lease obligation (Note 10)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -19910,7 +19912,11 @@
           <t>Deferred tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -22782,7 +22788,11 @@
           <t>Deferred tax expense 14</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23744,7 +23754,11 @@
           <t>Deferred tax expense (Note 14)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -25050,7 +25064,11 @@
           <t>Deferred tax expense (recovery) (Note 15)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -31786,7 +31804,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -37404,7 +37426,11 @@
           <t>Total share-based compensation expense $</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
